--- a/affiliate_products.xlsx
+++ b/affiliate_products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harub\OneDrive\デスクトップ\釣り早見表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB31563C-6491-4C87-86AA-CACB5681510C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{656F68E6-C6CB-4750-A1B2-5070FB14098A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{407C4F7D-1BC1-4FDE-A14D-06AEE72610EC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D019397B-3210-4D67-8A3B-E1564468B92E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="217">
   <si>
     <t>ID</t>
   </si>
@@ -288,40 +288,70 @@
     <t>7ft前後・UL〜L</t>
   </si>
   <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c30cb.e9b5cd4b.569c30cc.2ae5a817/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fnaturum%2F3056965%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>ソアレ BB メバリング</t>
+  </si>
+  <si>
+    <t>S610L</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c1367.468ae0af.569c1368.531b155e/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Ffishing-you%2F4969363334763%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>LT2000S-XH</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c2aea.3c718ba1.569c2aec.7f9fff91/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fcasting%2F4550133162640%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>月下美人 MX</t>
+  </si>
+  <si>
+    <t>6.5〜7.5ft・L前後</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c2aea.3c718ba1.569c2aec.7f9fff91/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fcasting%2F4550133338410%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>ソアレ XR メバリング</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569d3d17.32c04010.569d3d18.f33c3d6e/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fyokootsurigu%2F4969363334763%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c30cb.e9b5cd4b.569c30cc.2ae5a817/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fnaturum%2F3485714%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>6〜7ft前後・Lクラス</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c30cb.e9b5cd4b.569c30cc.2ae5a817/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fnaturum%2F3335847%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>ソアレ リミテッド</t>
+  </si>
+  <si>
+    <t>S76UL</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c30cb.e9b5cd4b.569c30cc.2ae5a817/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fnaturum%2F3485792%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569d7d5b.f460a5ec.569d7d5c.e12998cd/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fmarunishi%2F4969363049216%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>シーバス</t>
+  </si>
+  <si>
+    <t>ルアーニスト 86ML</t>
+  </si>
+  <si>
+    <t>86ML</t>
+  </si>
+  <si>
     <t>未設定</t>
-  </si>
-  <si>
-    <t>ソアレ BB メバリング</t>
-  </si>
-  <si>
-    <t>S610L</t>
-  </si>
-  <si>
-    <t>LT2000S-XH</t>
-  </si>
-  <si>
-    <t>月下美人 MX</t>
-  </si>
-  <si>
-    <t>6.5〜7.5ft・L前後</t>
-  </si>
-  <si>
-    <t>ソアレ XR メバリング</t>
-  </si>
-  <si>
-    <t>6〜7ft前後・Lクラス</t>
-  </si>
-  <si>
-    <t>ソアレ リミテッド メバリング</t>
-  </si>
-  <si>
-    <t>シーバス</t>
-  </si>
-  <si>
-    <t>ルアーニスト 86ML</t>
-  </si>
-  <si>
-    <t>86ML</t>
   </si>
   <si>
     <t>エクスセンス BB</t>
@@ -1026,7 +1056,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF59790-4364-431A-8A70-C3F0AEFD68DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40BFEAE-3785-4B40-BED5-DB3EF765185F}">
   <dimension ref="A1:I115"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1787,8 +1817,11 @@
       <c r="G26" t="s">
         <v>86</v>
       </c>
+      <c r="H26" t="s">
+        <v>87</v>
+      </c>
       <c r="I26" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
@@ -1813,8 +1846,11 @@
       <c r="G27" t="s">
         <v>89</v>
       </c>
+      <c r="H27" t="s">
+        <v>90</v>
+      </c>
       <c r="I27" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
@@ -1837,10 +1873,13 @@
         <v>57</v>
       </c>
       <c r="G28" t="s">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="H28" t="s">
+        <v>92</v>
       </c>
       <c r="I28" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
@@ -1865,8 +1904,11 @@
       <c r="G29" t="s">
         <v>60</v>
       </c>
+      <c r="H29" t="s">
+        <v>61</v>
+      </c>
       <c r="I29" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
@@ -1886,13 +1928,16 @@
         <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="H30" t="s">
+        <v>95</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
@@ -1912,13 +1957,16 @@
         <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G31" t="s">
         <v>89</v>
       </c>
+      <c r="H31" t="s">
+        <v>97</v>
+      </c>
       <c r="I31" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
@@ -1943,8 +1991,11 @@
       <c r="G32" t="s">
         <v>69</v>
       </c>
+      <c r="H32" t="s">
+        <v>70</v>
+      </c>
       <c r="I32" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.45">
@@ -1969,8 +2020,11 @@
       <c r="G33" t="s">
         <v>72</v>
       </c>
+      <c r="H33" t="s">
+        <v>98</v>
+      </c>
       <c r="I33" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
@@ -1993,10 +2047,13 @@
         <v>74</v>
       </c>
       <c r="G34" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+      <c r="H34" t="s">
+        <v>100</v>
       </c>
       <c r="I34" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
@@ -2016,13 +2073,16 @@
         <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G35" t="s">
-        <v>89</v>
+        <v>102</v>
+      </c>
+      <c r="H35" t="s">
+        <v>103</v>
       </c>
       <c r="I35" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
@@ -2047,8 +2107,11 @@
       <c r="G36" t="s">
         <v>80</v>
       </c>
+      <c r="H36" t="s">
+        <v>81</v>
+      </c>
       <c r="I36" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
@@ -2073,8 +2136,11 @@
       <c r="G37" t="s">
         <v>82</v>
       </c>
+      <c r="H37" t="s">
+        <v>104</v>
+      </c>
       <c r="I37" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.45">
@@ -2082,7 +2148,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
         <v>10</v>
@@ -2094,13 +2160,13 @@
         <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="G38" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I38" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
@@ -2108,7 +2174,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
         <v>10</v>
@@ -2120,13 +2186,13 @@
         <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G39" t="s">
         <v>33</v>
       </c>
       <c r="I39" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.45">
@@ -2134,7 +2200,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
         <v>10</v>
@@ -2149,10 +2215,10 @@
         <v>57</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I40" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.45">
@@ -2160,7 +2226,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
         <v>10</v>
@@ -2178,7 +2244,7 @@
         <v>26</v>
       </c>
       <c r="I41" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.45">
@@ -2186,7 +2252,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C42" t="s">
         <v>28</v>
@@ -2198,13 +2264,13 @@
         <v>12</v>
       </c>
       <c r="F42" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G42" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I42" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
@@ -2212,7 +2278,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
         <v>28</v>
@@ -2224,13 +2290,13 @@
         <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G43" t="s">
         <v>33</v>
       </c>
       <c r="I43" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
@@ -2238,7 +2304,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C44" t="s">
         <v>28</v>
@@ -2250,13 +2316,13 @@
         <v>12</v>
       </c>
       <c r="F44" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G44" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I44" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.45">
@@ -2264,7 +2330,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C45" t="s">
         <v>28</v>
@@ -2279,10 +2345,10 @@
         <v>38</v>
       </c>
       <c r="G45" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I45" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.45">
@@ -2290,7 +2356,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C46" t="s">
         <v>40</v>
@@ -2302,13 +2368,13 @@
         <v>12</v>
       </c>
       <c r="F46" t="s">
+        <v>117</v>
+      </c>
+      <c r="G46" t="s">
         <v>107</v>
       </c>
-      <c r="G46" t="s">
-        <v>98</v>
-      </c>
       <c r="I46" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.45">
@@ -2316,7 +2382,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C47" t="s">
         <v>40</v>
@@ -2328,13 +2394,13 @@
         <v>17</v>
       </c>
       <c r="F47" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="G47" t="s">
         <v>33</v>
       </c>
       <c r="I47" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
@@ -2342,7 +2408,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C48" t="s">
         <v>40</v>
@@ -2354,13 +2420,13 @@
         <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G48" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I48" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.45">
@@ -2368,7 +2434,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C49" t="s">
         <v>40</v>
@@ -2383,10 +2449,10 @@
         <v>48</v>
       </c>
       <c r="G49" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="I49" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.45">
@@ -2394,7 +2460,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C50" t="s">
         <v>10</v>
@@ -2406,13 +2472,13 @@
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G50" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I50" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.45">
@@ -2420,7 +2486,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
@@ -2432,13 +2498,13 @@
         <v>17</v>
       </c>
       <c r="F51" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="G51" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="I51" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.45">
@@ -2446,7 +2512,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
@@ -2461,10 +2527,10 @@
         <v>57</v>
       </c>
       <c r="G52" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="I52" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.45">
@@ -2472,7 +2538,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C53" t="s">
         <v>10</v>
@@ -2484,13 +2550,13 @@
         <v>17</v>
       </c>
       <c r="F53" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="G53" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="I53" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.45">
@@ -2498,7 +2564,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C54" t="s">
         <v>28</v>
@@ -2510,13 +2576,13 @@
         <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G54" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="I54" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.45">
@@ -2524,7 +2590,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C55" t="s">
         <v>28</v>
@@ -2536,13 +2602,13 @@
         <v>17</v>
       </c>
       <c r="F55" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G55" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I55" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.45">
@@ -2550,7 +2616,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C56" t="s">
         <v>28</v>
@@ -2562,13 +2628,13 @@
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G56" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="I56" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.45">
@@ -2576,7 +2642,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C57" t="s">
         <v>28</v>
@@ -2591,10 +2657,10 @@
         <v>38</v>
       </c>
       <c r="G57" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="I57" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.45">
@@ -2602,7 +2668,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C58" t="s">
         <v>40</v>
@@ -2614,13 +2680,13 @@
         <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G58" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="I58" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.45">
@@ -2628,7 +2694,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C59" t="s">
         <v>40</v>
@@ -2640,13 +2706,13 @@
         <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G59" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="I59" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.45">
@@ -2654,7 +2720,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C60" t="s">
         <v>40</v>
@@ -2666,13 +2732,13 @@
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G60" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="I60" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.45">
@@ -2680,7 +2746,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C61" t="s">
         <v>40</v>
@@ -2692,13 +2758,13 @@
         <v>17</v>
       </c>
       <c r="F61" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G61" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="I61" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.45">
@@ -2706,7 +2772,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C62" t="s">
         <v>10</v>
@@ -2718,13 +2784,13 @@
         <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G62" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I62" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.45">
@@ -2732,7 +2798,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C63" t="s">
         <v>10</v>
@@ -2744,13 +2810,13 @@
         <v>17</v>
       </c>
       <c r="F63" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="G63" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="I63" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.45">
@@ -2758,7 +2824,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C64" t="s">
         <v>10</v>
@@ -2770,13 +2836,13 @@
         <v>12</v>
       </c>
       <c r="F64" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="G64" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="I64" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.45">
@@ -2784,7 +2850,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C65" t="s">
         <v>10</v>
@@ -2796,13 +2862,13 @@
         <v>17</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="G65" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="I65" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.45">
@@ -2810,7 +2876,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C66" t="s">
         <v>28</v>
@@ -2822,13 +2888,13 @@
         <v>12</v>
       </c>
       <c r="F66" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="G66" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I66" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.45">
@@ -2836,7 +2902,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C67" t="s">
         <v>28</v>
@@ -2848,13 +2914,13 @@
         <v>17</v>
       </c>
       <c r="F67" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G67" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="I67" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.45">
@@ -2862,7 +2928,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C68" t="s">
         <v>28</v>
@@ -2874,13 +2940,13 @@
         <v>12</v>
       </c>
       <c r="F68" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G68" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="I68" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.45">
@@ -2888,7 +2954,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C69" t="s">
         <v>28</v>
@@ -2900,13 +2966,13 @@
         <v>17</v>
       </c>
       <c r="F69" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G69" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="I69" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.45">
@@ -2914,7 +2980,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C70" t="s">
         <v>40</v>
@@ -2926,13 +2992,13 @@
         <v>12</v>
       </c>
       <c r="F70" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G70" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="I70" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.45">
@@ -2940,7 +3006,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C71" t="s">
         <v>40</v>
@@ -2952,13 +3018,13 @@
         <v>17</v>
       </c>
       <c r="F71" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G71" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I71" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.45">
@@ -2966,7 +3032,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C72" t="s">
         <v>40</v>
@@ -2978,13 +3044,13 @@
         <v>12</v>
       </c>
       <c r="F72" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G72" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="I72" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.45">
@@ -2992,7 +3058,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C73" t="s">
         <v>40</v>
@@ -3004,13 +3070,13 @@
         <v>17</v>
       </c>
       <c r="F73" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G73" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="I73" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.45">
@@ -3018,7 +3084,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C74" t="s">
         <v>10</v>
@@ -3030,13 +3096,13 @@
         <v>12</v>
       </c>
       <c r="F74" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G74" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="I74" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.45">
@@ -3044,7 +3110,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C75" t="s">
         <v>10</v>
@@ -3056,13 +3122,13 @@
         <v>17</v>
       </c>
       <c r="F75" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="G75" t="s">
         <v>89</v>
       </c>
       <c r="I75" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.45">
@@ -3070,7 +3136,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
@@ -3088,7 +3154,7 @@
         <v>23</v>
       </c>
       <c r="I76" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.45">
@@ -3096,7 +3162,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C77" t="s">
         <v>10</v>
@@ -3114,7 +3180,7 @@
         <v>26</v>
       </c>
       <c r="I77" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.45">
@@ -3122,7 +3188,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C78" t="s">
         <v>28</v>
@@ -3134,13 +3200,13 @@
         <v>12</v>
       </c>
       <c r="F78" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="G78" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="I78" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.45">
@@ -3148,7 +3214,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C79" t="s">
         <v>28</v>
@@ -3160,13 +3226,13 @@
         <v>17</v>
       </c>
       <c r="F79" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="G79" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="I79" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.45">
@@ -3174,7 +3240,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C80" t="s">
         <v>28</v>
@@ -3186,13 +3252,13 @@
         <v>12</v>
       </c>
       <c r="F80" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G80" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I80" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.45">
@@ -3200,7 +3266,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C81" t="s">
         <v>28</v>
@@ -3218,7 +3284,7 @@
         <v>26</v>
       </c>
       <c r="I81" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.45">
@@ -3226,7 +3292,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C82" t="s">
         <v>40</v>
@@ -3238,13 +3304,13 @@
         <v>12</v>
       </c>
       <c r="F82" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="G82" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="I82" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.45">
@@ -3252,7 +3318,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C83" t="s">
         <v>40</v>
@@ -3264,13 +3330,13 @@
         <v>17</v>
       </c>
       <c r="F83" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G83" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="I83" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.45">
@@ -3278,7 +3344,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C84" t="s">
         <v>40</v>
@@ -3290,13 +3356,13 @@
         <v>12</v>
       </c>
       <c r="F84" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G84" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I84" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.45">
@@ -3304,7 +3370,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C85" t="s">
         <v>40</v>
@@ -3316,13 +3382,13 @@
         <v>17</v>
       </c>
       <c r="F85" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G85" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="I85" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.45">
@@ -3330,7 +3396,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C86" t="s">
         <v>10</v>
@@ -3342,13 +3408,13 @@
         <v>12</v>
       </c>
       <c r="F86" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G86" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="I86" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.45">
@@ -3356,7 +3422,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C87" t="s">
         <v>10</v>
@@ -3368,13 +3434,13 @@
         <v>17</v>
       </c>
       <c r="F87" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G87" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="I87" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.45">
@@ -3382,7 +3448,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C88" t="s">
         <v>10</v>
@@ -3394,13 +3460,13 @@
         <v>12</v>
       </c>
       <c r="F88" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="G88" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I88" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.45">
@@ -3408,7 +3474,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C89" t="s">
         <v>10</v>
@@ -3420,13 +3486,13 @@
         <v>17</v>
       </c>
       <c r="F89" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="G89" t="s">
         <v>26</v>
       </c>
       <c r="I89" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.45">
@@ -3434,7 +3500,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C90" t="s">
         <v>28</v>
@@ -3446,13 +3512,13 @@
         <v>12</v>
       </c>
       <c r="F90" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G90" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="I90" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.45">
@@ -3460,7 +3526,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C91" t="s">
         <v>28</v>
@@ -3472,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="F91" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="G91" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="I91" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.45">
@@ -3486,7 +3552,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C92" t="s">
         <v>28</v>
@@ -3498,13 +3564,13 @@
         <v>12</v>
       </c>
       <c r="F92" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G92" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="I92" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.45">
@@ -3512,7 +3578,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C93" t="s">
         <v>28</v>
@@ -3524,13 +3590,13 @@
         <v>17</v>
       </c>
       <c r="F93" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="G93" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="I93" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.45">
@@ -3538,7 +3604,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C94" t="s">
         <v>40</v>
@@ -3550,13 +3616,13 @@
         <v>12</v>
       </c>
       <c r="F94" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="G94" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="I94" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.45">
@@ -3564,7 +3630,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C95" t="s">
         <v>40</v>
@@ -3576,13 +3642,13 @@
         <v>17</v>
       </c>
       <c r="F95" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G95" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="I95" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.45">
@@ -3590,7 +3656,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C96" t="s">
         <v>40</v>
@@ -3602,13 +3668,13 @@
         <v>12</v>
       </c>
       <c r="F96" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="G96" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="I96" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.45">
@@ -3616,7 +3682,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C97" t="s">
         <v>40</v>
@@ -3628,13 +3694,13 @@
         <v>17</v>
       </c>
       <c r="F97" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G97" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="I97" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.45">
@@ -3642,7 +3708,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C98" t="s">
         <v>10</v>
@@ -3654,13 +3720,13 @@
         <v>12</v>
       </c>
       <c r="F98" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="G98" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="I98" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.45">
@@ -3668,7 +3734,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C99" t="s">
         <v>10</v>
@@ -3680,13 +3746,13 @@
         <v>17</v>
       </c>
       <c r="F99" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G99" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I99" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.45">
@@ -3694,7 +3760,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C100" t="s">
         <v>10</v>
@@ -3712,7 +3778,7 @@
         <v>23</v>
       </c>
       <c r="I100" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.45">
@@ -3720,7 +3786,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C101" t="s">
         <v>10</v>
@@ -3732,13 +3798,13 @@
         <v>17</v>
       </c>
       <c r="F101" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="G101" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="I101" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.45">
@@ -3746,7 +3812,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C102" t="s">
         <v>28</v>
@@ -3758,13 +3824,13 @@
         <v>12</v>
       </c>
       <c r="F102" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G102" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="I102" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.45">
@@ -3772,7 +3838,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C103" t="s">
         <v>28</v>
@@ -3784,13 +3850,13 @@
         <v>17</v>
       </c>
       <c r="F103" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G103" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="I103" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.45">
@@ -3798,7 +3864,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C104" t="s">
         <v>28</v>
@@ -3810,13 +3876,13 @@
         <v>12</v>
       </c>
       <c r="F104" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G104" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="I104" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.45">
@@ -3824,7 +3890,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C105" t="s">
         <v>28</v>
@@ -3836,13 +3902,13 @@
         <v>17</v>
       </c>
       <c r="F105" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="G105" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="I105" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.45">
@@ -3850,7 +3916,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C106" t="s">
         <v>40</v>
@@ -3862,13 +3928,13 @@
         <v>12</v>
       </c>
       <c r="F106" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="G106" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="I106" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.45">
@@ -3876,7 +3942,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C107" t="s">
         <v>40</v>
@@ -3888,13 +3954,13 @@
         <v>17</v>
       </c>
       <c r="F107" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G107" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="I107" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.45">
@@ -3902,7 +3968,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C108" t="s">
         <v>40</v>
@@ -3914,13 +3980,13 @@
         <v>12</v>
       </c>
       <c r="F108" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G108" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="I108" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.45">
@@ -3928,7 +3994,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C109" t="s">
         <v>40</v>
@@ -3940,13 +4006,13 @@
         <v>17</v>
       </c>
       <c r="F109" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G109" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="I109" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.45">
@@ -3954,7 +4020,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C110" t="s">
         <v>10</v>
@@ -3966,13 +4032,13 @@
         <v>12</v>
       </c>
       <c r="F110" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="G110" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="I110" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.45">
@@ -3980,7 +4046,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C111" t="s">
         <v>10</v>
@@ -3992,13 +4058,13 @@
         <v>17</v>
       </c>
       <c r="F111" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="G111" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="I111" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.45">
@@ -4006,7 +4072,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C112" t="s">
         <v>28</v>
@@ -4018,13 +4084,13 @@
         <v>12</v>
       </c>
       <c r="F112" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G112" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="I112" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.45">
@@ -4032,7 +4098,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C113" t="s">
         <v>28</v>
@@ -4044,13 +4110,13 @@
         <v>17</v>
       </c>
       <c r="F113" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="G113" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="I113" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.45">
@@ -4058,7 +4124,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C114" t="s">
         <v>40</v>
@@ -4070,13 +4136,13 @@
         <v>12</v>
       </c>
       <c r="F114" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="G114" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="I114" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.45">
@@ -4084,7 +4150,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C115" t="s">
         <v>40</v>
@@ -4096,13 +4162,13 @@
         <v>17</v>
       </c>
       <c r="F115" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G115" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="I115" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/affiliate_products.xlsx
+++ b/affiliate_products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harub\OneDrive\デスクトップ\釣り早見表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{656F68E6-C6CB-4750-A1B2-5070FB14098A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7112ED8D-9BE0-4A6A-9A8A-E27F23BB7FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{D019397B-3210-4D67-8A3B-E1564468B92E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CCF25F6E-492B-475D-9336-37A5B8C3677C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="218">
   <si>
     <t>ID</t>
   </si>
@@ -291,211 +291,214 @@
     <t>https://hb.afl.rakuten.co.jp/ichiba/569c30cb.e9b5cd4b.569c30cc.2ae5a817/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fnaturum%2F3056965%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
   </si>
   <si>
-    <t>ソアレ BB メバリング</t>
+    <t>ソアレ BB</t>
+  </si>
+  <si>
+    <t>S76UL</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c27c2.a90de95f.569c27c3.6b55682b/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fpoint%2F4969363333827%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>LT2000S-XH</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c2aea.3c718ba1.569c2aec.7f9fff91/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fcasting%2F4550133162640%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>月下美人 MX</t>
+  </si>
+  <si>
+    <t>6.5〜7.5ft・L前後</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c2aea.3c718ba1.569c2aec.7f9fff91/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fcasting%2F4550133338410%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>ソアレ XR</t>
+  </si>
+  <si>
+    <t>S68UL</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c27c2.a90de95f.569c27c3.6b55682b/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fpoint%2F4969363303813%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c30cb.e9b5cd4b.569c30cc.2ae5a817/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fnaturum%2F3485714%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>6〜7ft前後・Lクラス</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c30cb.e9b5cd4b.569c30cc.2ae5a817/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fnaturum%2F3335847%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>ソアレ リミテッド</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569c30cb.e9b5cd4b.569c30cc.2ae5a817/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fnaturum%2F3485792%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>https://hb.afl.rakuten.co.jp/ichiba/569d7d5b.f460a5ec.569d7d5c.e12998cd/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fmarunishi%2F4969363049216%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
+  </si>
+  <si>
+    <t>シーバス</t>
+  </si>
+  <si>
+    <t>ルアーニスト 86ML</t>
+  </si>
+  <si>
+    <t>86ML</t>
+  </si>
+  <si>
+    <t>未設定</t>
+  </si>
+  <si>
+    <t>エクスセンス BB</t>
+  </si>
+  <si>
+    <t>LT3000-CXH</t>
+  </si>
+  <si>
+    <t>ラテオ 86ML・K</t>
+  </si>
+  <si>
+    <t>86ML・K</t>
+  </si>
+  <si>
+    <t>エクスセンス ジェノス</t>
+  </si>
+  <si>
+    <t>セルテート LT3000-XH</t>
+  </si>
+  <si>
+    <t>LT3000-XH</t>
+  </si>
+  <si>
+    <t>C3000MHG</t>
+  </si>
+  <si>
+    <t>モアザン 86ML</t>
+  </si>
+  <si>
+    <t>エクスセンス ∞(インフィニティ)</t>
+  </si>
+  <si>
+    <t>ライトショアジギング</t>
+  </si>
+  <si>
+    <t>ルアーニスト 96M</t>
+  </si>
+  <si>
+    <t>96M</t>
+  </si>
+  <si>
+    <t>コルトスナイパー BB</t>
+  </si>
+  <si>
+    <t>S96M</t>
+  </si>
+  <si>
+    <t>LT4000-CXH</t>
+  </si>
+  <si>
+    <t>サハラ</t>
+  </si>
+  <si>
+    <t>C5000</t>
+  </si>
+  <si>
+    <t>ドラッガー X 96ML</t>
+  </si>
+  <si>
+    <t>96ML</t>
+  </si>
+  <si>
+    <t>コルトスナイパー XR</t>
+  </si>
+  <si>
+    <t>S96ML</t>
+  </si>
+  <si>
+    <t>レグザ LT4000-CXH</t>
+  </si>
+  <si>
+    <t>C5000XG</t>
+  </si>
+  <si>
+    <t>ドラッガー SX</t>
+  </si>
+  <si>
+    <t>9.6ft前後・ML〜M</t>
+  </si>
+  <si>
+    <t>S100MH</t>
+  </si>
+  <si>
+    <t>セルテート LT4000-CXH</t>
+  </si>
+  <si>
+    <t>ツインパワー SW</t>
+  </si>
+  <si>
+    <t>5000HG</t>
+  </si>
+  <si>
+    <t>ショアジギング</t>
+  </si>
+  <si>
+    <t>ショアジギング X 96M</t>
+  </si>
+  <si>
+    <t>24 レブロス</t>
+  </si>
+  <si>
+    <t>LT5000-CXH</t>
+  </si>
+  <si>
+    <t>ドラッガー X 96M</t>
+  </si>
+  <si>
+    <t>セルテート LT5000D-CXH</t>
+  </si>
+  <si>
+    <t>LT5000D-CXH</t>
+  </si>
+  <si>
+    <t>ストラディック SW</t>
+  </si>
+  <si>
+    <t>5000XG</t>
+  </si>
+  <si>
+    <t>9.6〜10.0ft・M〜MH</t>
+  </si>
+  <si>
+    <t>S100XH</t>
+  </si>
+  <si>
+    <t>セルテート SW 5000〜6000番クラス</t>
+  </si>
+  <si>
+    <t>SW 5000〜6000番クラス</t>
+  </si>
+  <si>
+    <t>5000〜8000HG</t>
+  </si>
+  <si>
+    <t>チニング</t>
+  </si>
+  <si>
+    <t>シルバーウルフ 73LML-S</t>
+  </si>
+  <si>
+    <t>73LML-S</t>
+  </si>
+  <si>
+    <t>ブレニアス BB</t>
   </si>
   <si>
     <t>S610L</t>
-  </si>
-  <si>
-    <t>https://hb.afl.rakuten.co.jp/ichiba/569c1367.468ae0af.569c1368.531b155e/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Ffishing-you%2F4969363334763%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
-  </si>
-  <si>
-    <t>LT2000S-XH</t>
-  </si>
-  <si>
-    <t>https://hb.afl.rakuten.co.jp/ichiba/569c2aea.3c718ba1.569c2aec.7f9fff91/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fcasting%2F4550133162640%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
-  </si>
-  <si>
-    <t>月下美人 MX</t>
-  </si>
-  <si>
-    <t>6.5〜7.5ft・L前後</t>
-  </si>
-  <si>
-    <t>https://hb.afl.rakuten.co.jp/ichiba/569c2aea.3c718ba1.569c2aec.7f9fff91/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fcasting%2F4550133338410%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
-  </si>
-  <si>
-    <t>ソアレ XR メバリング</t>
-  </si>
-  <si>
-    <t>https://hb.afl.rakuten.co.jp/ichiba/569d3d17.32c04010.569d3d18.f33c3d6e/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fyokootsurigu%2F4969363334763%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
-  </si>
-  <si>
-    <t>https://hb.afl.rakuten.co.jp/ichiba/569c30cb.e9b5cd4b.569c30cc.2ae5a817/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fnaturum%2F3485714%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
-  </si>
-  <si>
-    <t>6〜7ft前後・Lクラス</t>
-  </si>
-  <si>
-    <t>https://hb.afl.rakuten.co.jp/ichiba/569c30cb.e9b5cd4b.569c30cc.2ae5a817/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fnaturum%2F3335847%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
-  </si>
-  <si>
-    <t>ソアレ リミテッド</t>
-  </si>
-  <si>
-    <t>S76UL</t>
-  </si>
-  <si>
-    <t>https://hb.afl.rakuten.co.jp/ichiba/569c30cb.e9b5cd4b.569c30cc.2ae5a817/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fnaturum%2F3485792%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
-  </si>
-  <si>
-    <t>https://hb.afl.rakuten.co.jp/ichiba/569d7d5b.f460a5ec.569d7d5c.e12998cd/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fmarunishi%2F4969363049216%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
-  </si>
-  <si>
-    <t>シーバス</t>
-  </si>
-  <si>
-    <t>ルアーニスト 86ML</t>
-  </si>
-  <si>
-    <t>86ML</t>
-  </si>
-  <si>
-    <t>未設定</t>
-  </si>
-  <si>
-    <t>エクスセンス BB</t>
-  </si>
-  <si>
-    <t>LT3000-CXH</t>
-  </si>
-  <si>
-    <t>ラテオ 86ML・K</t>
-  </si>
-  <si>
-    <t>86ML・K</t>
-  </si>
-  <si>
-    <t>エクスセンス ジェノス</t>
-  </si>
-  <si>
-    <t>セルテート LT3000-XH</t>
-  </si>
-  <si>
-    <t>LT3000-XH</t>
-  </si>
-  <si>
-    <t>C3000MHG</t>
-  </si>
-  <si>
-    <t>モアザン 86ML</t>
-  </si>
-  <si>
-    <t>エクスセンス ∞(インフィニティ)</t>
-  </si>
-  <si>
-    <t>ライトショアジギング</t>
-  </si>
-  <si>
-    <t>ルアーニスト 96M</t>
-  </si>
-  <si>
-    <t>96M</t>
-  </si>
-  <si>
-    <t>コルトスナイパー BB</t>
-  </si>
-  <si>
-    <t>S96M</t>
-  </si>
-  <si>
-    <t>LT4000-CXH</t>
-  </si>
-  <si>
-    <t>サハラ</t>
-  </si>
-  <si>
-    <t>C5000</t>
-  </si>
-  <si>
-    <t>ドラッガー X 96ML</t>
-  </si>
-  <si>
-    <t>96ML</t>
-  </si>
-  <si>
-    <t>コルトスナイパー XR</t>
-  </si>
-  <si>
-    <t>S96ML</t>
-  </si>
-  <si>
-    <t>レグザ LT4000-CXH</t>
-  </si>
-  <si>
-    <t>C5000XG</t>
-  </si>
-  <si>
-    <t>ドラッガー SX</t>
-  </si>
-  <si>
-    <t>9.6ft前後・ML〜M</t>
-  </si>
-  <si>
-    <t>S100MH</t>
-  </si>
-  <si>
-    <t>セルテート LT4000-CXH</t>
-  </si>
-  <si>
-    <t>ツインパワー SW</t>
-  </si>
-  <si>
-    <t>5000HG</t>
-  </si>
-  <si>
-    <t>ショアジギング</t>
-  </si>
-  <si>
-    <t>ショアジギング X 96M</t>
-  </si>
-  <si>
-    <t>24 レブロス</t>
-  </si>
-  <si>
-    <t>LT5000-CXH</t>
-  </si>
-  <si>
-    <t>ドラッガー X 96M</t>
-  </si>
-  <si>
-    <t>セルテート LT5000D-CXH</t>
-  </si>
-  <si>
-    <t>LT5000D-CXH</t>
-  </si>
-  <si>
-    <t>ストラディック SW</t>
-  </si>
-  <si>
-    <t>5000XG</t>
-  </si>
-  <si>
-    <t>9.6〜10.0ft・M〜MH</t>
-  </si>
-  <si>
-    <t>S100XH</t>
-  </si>
-  <si>
-    <t>セルテート SW 5000〜6000番クラス</t>
-  </si>
-  <si>
-    <t>SW 5000〜6000番クラス</t>
-  </si>
-  <si>
-    <t>5000〜8000HG</t>
-  </si>
-  <si>
-    <t>チニング</t>
-  </si>
-  <si>
-    <t>シルバーウルフ 73LML-S</t>
-  </si>
-  <si>
-    <t>73LML-S</t>
-  </si>
-  <si>
-    <t>ブレニアス BB</t>
   </si>
   <si>
     <t>シルバーウルフ MX 82ML</t>
@@ -1056,7 +1059,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40BFEAE-3785-4B40-BED5-DB3EF765185F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1683FB58-8F48-4CFC-8796-B4A88F3F9541}">
   <dimension ref="A1:I115"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1960,10 +1963,10 @@
         <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I31" t="s">
         <v>16</v>
@@ -2021,7 +2024,7 @@
         <v>72</v>
       </c>
       <c r="H33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I33" t="s">
         <v>16</v>
@@ -2047,10 +2050,10 @@
         <v>74</v>
       </c>
       <c r="G34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I34" t="s">
         <v>16</v>
@@ -2073,10 +2076,10 @@
         <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G35" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s">
         <v>103</v>
@@ -3125,7 +3128,7 @@
         <v>156</v>
       </c>
       <c r="G75" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="I75" t="s">
         <v>108</v>
@@ -3200,10 +3203,10 @@
         <v>12</v>
       </c>
       <c r="F78" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G78" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I78" t="s">
         <v>108</v>
@@ -3229,7 +3232,7 @@
         <v>156</v>
       </c>
       <c r="G79" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I79" t="s">
         <v>108</v>
@@ -3252,7 +3255,7 @@
         <v>12</v>
       </c>
       <c r="F80" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G80" t="s">
         <v>115</v>
@@ -3304,10 +3307,10 @@
         <v>12</v>
       </c>
       <c r="F82" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G82" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I82" t="s">
         <v>108</v>
@@ -3330,10 +3333,10 @@
         <v>17</v>
       </c>
       <c r="F83" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G83" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I83" t="s">
         <v>108</v>
@@ -3356,10 +3359,10 @@
         <v>12</v>
       </c>
       <c r="F84" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G84" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I84" t="s">
         <v>108</v>
@@ -3382,10 +3385,10 @@
         <v>17</v>
       </c>
       <c r="F85" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G85" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I85" t="s">
         <v>108</v>
@@ -3396,7 +3399,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C86" t="s">
         <v>10</v>
@@ -3408,10 +3411,10 @@
         <v>12</v>
       </c>
       <c r="F86" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G86" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I86" t="s">
         <v>108</v>
@@ -3422,7 +3425,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C87" t="s">
         <v>10</v>
@@ -3434,10 +3437,10 @@
         <v>17</v>
       </c>
       <c r="F87" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G87" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I87" t="s">
         <v>108</v>
@@ -3448,7 +3451,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C88" t="s">
         <v>10</v>
@@ -3474,7 +3477,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C89" t="s">
         <v>10</v>
@@ -3500,7 +3503,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C90" t="s">
         <v>28</v>
@@ -3512,10 +3515,10 @@
         <v>12</v>
       </c>
       <c r="F90" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G90" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I90" t="s">
         <v>108</v>
@@ -3526,7 +3529,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C91" t="s">
         <v>28</v>
@@ -3538,10 +3541,10 @@
         <v>17</v>
       </c>
       <c r="F91" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G91" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I91" t="s">
         <v>108</v>
@@ -3552,7 +3555,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C92" t="s">
         <v>28</v>
@@ -3564,10 +3567,10 @@
         <v>12</v>
       </c>
       <c r="F92" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G92" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I92" t="s">
         <v>108</v>
@@ -3578,7 +3581,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C93" t="s">
         <v>28</v>
@@ -3590,10 +3593,10 @@
         <v>17</v>
       </c>
       <c r="F93" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I93" t="s">
         <v>108</v>
@@ -3604,7 +3607,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C94" t="s">
         <v>40</v>
@@ -3616,10 +3619,10 @@
         <v>12</v>
       </c>
       <c r="F94" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G94" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I94" t="s">
         <v>108</v>
@@ -3630,7 +3633,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C95" t="s">
         <v>40</v>
@@ -3642,10 +3645,10 @@
         <v>17</v>
       </c>
       <c r="F95" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G95" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I95" t="s">
         <v>108</v>
@@ -3656,7 +3659,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C96" t="s">
         <v>40</v>
@@ -3668,10 +3671,10 @@
         <v>12</v>
       </c>
       <c r="F96" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G96" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I96" t="s">
         <v>108</v>
@@ -3682,7 +3685,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C97" t="s">
         <v>40</v>
@@ -3694,10 +3697,10 @@
         <v>17</v>
       </c>
       <c r="F97" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G97" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I97" t="s">
         <v>108</v>
@@ -3708,7 +3711,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C98" t="s">
         <v>10</v>
@@ -3720,10 +3723,10 @@
         <v>12</v>
       </c>
       <c r="F98" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G98" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I98" t="s">
         <v>108</v>
@@ -3734,7 +3737,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C99" t="s">
         <v>10</v>
@@ -3746,10 +3749,10 @@
         <v>17</v>
       </c>
       <c r="F99" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G99" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I99" t="s">
         <v>108</v>
@@ -3760,7 +3763,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C100" t="s">
         <v>10</v>
@@ -3786,7 +3789,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C101" t="s">
         <v>10</v>
@@ -3801,7 +3804,7 @@
         <v>125</v>
       </c>
       <c r="G101" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I101" t="s">
         <v>108</v>
@@ -3812,7 +3815,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C102" t="s">
         <v>28</v>
@@ -3824,10 +3827,10 @@
         <v>12</v>
       </c>
       <c r="F102" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G102" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I102" t="s">
         <v>108</v>
@@ -3838,7 +3841,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C103" t="s">
         <v>28</v>
@@ -3850,10 +3853,10 @@
         <v>17</v>
       </c>
       <c r="F103" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G103" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I103" t="s">
         <v>108</v>
@@ -3864,7 +3867,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C104" t="s">
         <v>28</v>
@@ -3876,10 +3879,10 @@
         <v>12</v>
       </c>
       <c r="F104" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G104" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I104" t="s">
         <v>108</v>
@@ -3890,7 +3893,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C105" t="s">
         <v>28</v>
@@ -3902,10 +3905,10 @@
         <v>17</v>
       </c>
       <c r="F105" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G105" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I105" t="s">
         <v>108</v>
@@ -3916,7 +3919,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C106" t="s">
         <v>40</v>
@@ -3928,10 +3931,10 @@
         <v>12</v>
       </c>
       <c r="F106" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G106" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I106" t="s">
         <v>108</v>
@@ -3942,7 +3945,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C107" t="s">
         <v>40</v>
@@ -3954,10 +3957,10 @@
         <v>17</v>
       </c>
       <c r="F107" t="s">
+        <v>202</v>
+      </c>
+      <c r="G107" t="s">
         <v>201</v>
-      </c>
-      <c r="G107" t="s">
-        <v>200</v>
       </c>
       <c r="I107" t="s">
         <v>108</v>
@@ -3968,7 +3971,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C108" t="s">
         <v>40</v>
@@ -3980,10 +3983,10 @@
         <v>12</v>
       </c>
       <c r="F108" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G108" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I108" t="s">
         <v>108</v>
@@ -3994,7 +3997,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C109" t="s">
         <v>40</v>
@@ -4006,10 +4009,10 @@
         <v>17</v>
       </c>
       <c r="F109" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G109" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I109" t="s">
         <v>108</v>
@@ -4020,7 +4023,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C110" t="s">
         <v>10</v>
@@ -4032,10 +4035,10 @@
         <v>12</v>
       </c>
       <c r="F110" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G110" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I110" t="s">
         <v>108</v>
@@ -4046,7 +4049,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C111" t="s">
         <v>10</v>
@@ -4058,10 +4061,10 @@
         <v>17</v>
       </c>
       <c r="F111" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G111" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I111" t="s">
         <v>108</v>
@@ -4072,7 +4075,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C112" t="s">
         <v>28</v>
@@ -4084,10 +4087,10 @@
         <v>12</v>
       </c>
       <c r="F112" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G112" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I112" t="s">
         <v>108</v>
@@ -4098,7 +4101,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C113" t="s">
         <v>28</v>
@@ -4110,10 +4113,10 @@
         <v>17</v>
       </c>
       <c r="F113" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G113" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I113" t="s">
         <v>108</v>
@@ -4124,7 +4127,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C114" t="s">
         <v>40</v>
@@ -4136,10 +4139,10 @@
         <v>12</v>
       </c>
       <c r="F114" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G114" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I114" t="s">
         <v>108</v>
@@ -4150,7 +4153,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C115" t="s">
         <v>40</v>
@@ -4162,10 +4165,10 @@
         <v>17</v>
       </c>
       <c r="F115" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G115" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I115" t="s">
         <v>108</v>

--- a/affiliate_products.xlsx
+++ b/affiliate_products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harub\OneDrive\デスクトップ\釣り早見表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7112ED8D-9BE0-4A6A-9A8A-E27F23BB7FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02C9BC62-211A-42EB-A4C3-8E326FD6F848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{CCF25F6E-492B-475D-9336-37A5B8C3677C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{4ECE0008-7EAA-4728-A452-0FEB62F13A25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -162,6 +162,9 @@
     <t>セフィア リミテッド</t>
   </si>
   <si>
+    <t>S90ML</t>
+  </si>
+  <si>
     <t>https://hb.afl.rakuten.co.jp/ichiba/569c27c2.a90de95f.569c27c3.6b55682b/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fpoint%2F4969363358653%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
   </si>
   <si>
@@ -222,7 +225,7 @@
     <t>https://hb.afl.rakuten.co.jp/ichiba/569c2aea.3c718ba1.569c2aec.7f9fff91/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fcasting%2F4550133338311%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
   </si>
   <si>
-    <t>ソアレ XR アジング</t>
+    <t>ソアレ SS アジング</t>
   </si>
   <si>
     <t>S64L</t>
@@ -271,9 +274,6 @@
   </si>
   <si>
     <t>https://hb.afl.rakuten.co.jp/ichiba/569c2aea.3c718ba1.569c2aec.7f9fff91/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fcasting%2F4550133110573%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
-  </si>
-  <si>
-    <t>C2000SS</t>
   </si>
   <si>
     <t>https://hb.afl.rakuten.co.jp/ichiba/569c30cb.e9b5cd4b.569c30cc.2ae5a817/?pc=https%3A%2F%2Fitem.rakuten.co.jp%2Fnaturum%2F3456112%2F&amp;link_type=text&amp;ut=eyJwYWdlIjoiaXRlbSIsInR5cGUiOiJ0ZXh0Iiwic2l6ZSI6IjI0MHgyNDAiLCJuYW0iOjEsIm5hbXAiOiJyaWdodCIsImNvbSI6MSwiY29tcCI6ImRvd24iLCJwcmljZSI6MCwiYm9yIjoxLCJjb2wiOjEsImJidG4iOjEsInByb2QiOjAsImFtcCI6ZmFsc2V9</t>
@@ -1059,7 +1059,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1683FB58-8F48-4CFC-8796-B4A88F3F9541}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D05F823-9245-4139-A971-F94CD102246F}">
   <dimension ref="A1:I115"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1383,10 +1383,10 @@
         <v>44</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I11" t="s">
         <v>16</v>
@@ -1409,13 +1409,13 @@
         <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" t="s">
         <v>36</v>
       </c>
       <c r="H12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I12" t="s">
         <v>16</v>
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
         <v>26</v>
       </c>
       <c r="H13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I13" t="s">
         <v>16</v>
@@ -1455,7 +1455,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -1467,13 +1467,13 @@
         <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I14" t="s">
         <v>16</v>
@@ -1484,7 +1484,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -1496,13 +1496,13 @@
         <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I15" t="s">
         <v>16</v>
@@ -1513,7 +1513,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -1525,13 +1525,13 @@
         <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I16" t="s">
         <v>16</v>
@@ -1542,7 +1542,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
         <v>10</v>
@@ -1557,10 +1557,10 @@
         <v>25</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I17" t="s">
         <v>16</v>
@@ -1571,7 +1571,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C18" t="s">
         <v>28</v>
@@ -1583,13 +1583,13 @@
         <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I18" t="s">
         <v>16</v>
@@ -1600,7 +1600,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
         <v>28</v>
@@ -1612,13 +1612,13 @@
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I19" t="s">
         <v>16</v>
@@ -1629,7 +1629,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
         <v>28</v>
@@ -1641,13 +1641,13 @@
         <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I20" t="s">
         <v>16</v>
@@ -1658,7 +1658,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
         <v>28</v>
@@ -1670,13 +1670,13 @@
         <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I21" t="s">
         <v>16</v>
@@ -1687,7 +1687,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
         <v>40</v>
@@ -1699,13 +1699,13 @@
         <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I22" t="s">
         <v>16</v>
@@ -1716,7 +1716,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
         <v>40</v>
@@ -1728,13 +1728,13 @@
         <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s">
         <v>16</v>
@@ -1745,7 +1745,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
         <v>40</v>
@@ -1757,13 +1757,13 @@
         <v>12</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s">
         <v>16</v>
@@ -1774,7 +1774,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C25" t="s">
         <v>40</v>
@@ -1786,10 +1786,10 @@
         <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G25" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="H25" t="s">
         <v>83</v>
@@ -1873,7 +1873,7 @@
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G28" t="s">
         <v>91</v>
@@ -1905,10 +1905,10 @@
         <v>25</v>
       </c>
       <c r="G29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I29" t="s">
         <v>16</v>
@@ -1989,13 +1989,13 @@
         <v>12</v>
       </c>
       <c r="F32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I32" t="s">
         <v>16</v>
@@ -2018,10 +2018,10 @@
         <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H33" t="s">
         <v>99</v>
@@ -2047,7 +2047,7 @@
         <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s">
         <v>100</v>
@@ -2105,13 +2105,13 @@
         <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s">
         <v>16</v>
@@ -2134,10 +2134,10 @@
         <v>17</v>
       </c>
       <c r="F37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G37" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="H37" t="s">
         <v>104</v>
@@ -2215,7 +2215,7 @@
         <v>12</v>
       </c>
       <c r="F40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G40" t="s">
         <v>110</v>
@@ -2449,7 +2449,7 @@
         <v>17</v>
       </c>
       <c r="F49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G49" t="s">
         <v>116</v>
@@ -2527,7 +2527,7 @@
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G52" t="s">
         <v>124</v>
@@ -3151,7 +3151,7 @@
         <v>12</v>
       </c>
       <c r="F76" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G76" t="s">
         <v>23</v>
@@ -3775,7 +3775,7 @@
         <v>12</v>
       </c>
       <c r="F100" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G100" t="s">
         <v>23</v>
